--- a/multi seed generators/merged 10 seeds/regression/results/aggregated/all_metrics_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/regression/results/aggregated/all_metrics_mean_sd.xlsx
@@ -333,12 +333,10 @@
       <c r="O3" t="n">
         <v>0.0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P3"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -1257,11 +1255,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R16" s="2" t="n">
@@ -1470,11 +1468,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -1683,11 +1681,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R22" s="2" t="n">
@@ -1895,12 +1893,10 @@
       <c r="O25" t="n">
         <v>0.0</v>
       </c>
-      <c r="P25" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P25"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -2819,11 +2815,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R38" s="2" t="n">
@@ -3032,11 +3028,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P41" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -3245,11 +3241,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R44" s="2" t="n">
@@ -3457,12 +3453,10 @@
       <c r="O47" t="n">
         <v>0.0</v>
       </c>
-      <c r="P47" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P47"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -4381,11 +4375,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R60" s="2" t="n">
@@ -4594,11 +4588,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -4807,11 +4801,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R66" s="2" t="n">
@@ -5019,12 +5013,10 @@
       <c r="O69" t="n">
         <v>0.0</v>
       </c>
-      <c r="P69" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P69"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -5943,11 +5935,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R82" s="2" t="n">
@@ -6156,11 +6148,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -6369,11 +6361,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R88" s="2" t="n">
@@ -6581,12 +6573,10 @@
       <c r="O91" t="n">
         <v>0.0</v>
       </c>
-      <c r="P91" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P91"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -6794,12 +6784,10 @@
       <c r="O94" s="2" t="n">
         <v>0.6350429577102925</v>
       </c>
-      <c r="P94" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P94" s="2"/>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.635043 ± 0</t>
+          <t xml:space="preserve">0.635043</t>
         </is>
       </c>
       <c r="R94" s="2" t="n">
@@ -6865,12 +6853,10 @@
       <c r="O95" t="n">
         <v>0.234001770082493</v>
       </c>
-      <c r="P95" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P95"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.234002 ± 0</t>
+          <t xml:space="preserve">0.234002</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -6936,12 +6922,10 @@
       <c r="O96" s="2" t="n">
         <v>0.7538892658400576</v>
       </c>
-      <c r="P96" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P96" s="2"/>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753889 ± 0</t>
+          <t xml:space="preserve">0.753889</t>
         </is>
       </c>
       <c r="R96" s="2" t="n">
@@ -7007,12 +6991,10 @@
       <c r="O97" t="n">
         <v>103.3663040262217</v>
       </c>
-      <c r="P97" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P97"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t xml:space="preserve">103.366 ± 0</t>
+          <t xml:space="preserve">103.366</t>
         </is>
       </c>
       <c r="R97" t="n">
@@ -7078,12 +7060,10 @@
       <c r="O98" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P98" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P98" s="2"/>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R98" s="2" t="n">
@@ -7149,12 +7129,10 @@
       <c r="O99" t="n">
         <v>15.28669699143929</v>
       </c>
-      <c r="P99" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P99"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.2867 ± 0</t>
+          <t xml:space="preserve">15.2867</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -7220,12 +7198,10 @@
       <c r="O100" s="2" t="n">
         <v>15.28669699143929</v>
       </c>
-      <c r="P100" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P100" s="2"/>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.2867 ± 0</t>
+          <t xml:space="preserve">15.2867</t>
         </is>
       </c>
       <c r="R100" s="2" t="n">
@@ -7291,12 +7267,10 @@
       <c r="O101" t="n">
         <v>14.47097656386145</v>
       </c>
-      <c r="P101" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P101"/>
       <c r="Q101" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.471 ± 0</t>
+          <t xml:space="preserve">14.471</t>
         </is>
       </c>
       <c r="R101" t="n">
@@ -7362,12 +7336,10 @@
       <c r="O102" s="2" t="n">
         <v>0.9447941295445619</v>
       </c>
-      <c r="P102" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P102" s="2"/>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.944794 ± 0</t>
+          <t xml:space="preserve">0.944794</t>
         </is>
       </c>
       <c r="R102" s="2" t="n">
@@ -7434,11 +7406,11 @@
         <v>3.2300671118926934</v>
       </c>
       <c r="P103" t="n">
-        <v>0.0</v>
+        <v>0.41216680506041453</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.23007 ± 0</t>
+          <t xml:space="preserve">3.23007 ± 0.412167</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -7505,11 +7477,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R104" s="2" t="n">
@@ -7576,11 +7548,11 @@
         <v>3.605952757328024</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0</v>
+        <v>0.1660113521529581</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.60595 ± 0</t>
+          <t xml:space="preserve">3.60595 ± 0.166011</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -7647,11 +7619,11 @@
         <v>0.074916165247085</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>0.0</v>
+        <v>0.059340847416627165</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0749162 ± 0</t>
+          <t xml:space="preserve">0.0749162 ± 0.0593408</t>
         </is>
       </c>
       <c r="R106" s="2" t="n">
@@ -7718,11 +7690,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P107" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -7789,11 +7761,11 @@
         <v>0.9247419656410022</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>0.0</v>
+        <v>0.059339811560804166</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.924742 ± 0</t>
+          <t xml:space="preserve">0.924742 ± 0.0593398</t>
         </is>
       </c>
       <c r="R108" s="2" t="n">
@@ -7860,11 +7832,11 @@
         <v>9.096777018801081</v>
       </c>
       <c r="P109" t="n">
-        <v>0.0</v>
+        <v>4.633987147057834</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.09678 ± 0</t>
+          <t xml:space="preserve">9.09678 ± 4.63399</t>
         </is>
       </c>
       <c r="R109" t="n">
@@ -7931,11 +7903,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R110" s="2" t="n">
@@ -8002,11 +7974,11 @@
         <v>9.609014699568137</v>
       </c>
       <c r="P111" t="n">
-        <v>0.0</v>
+        <v>4.605666584232684</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.60901 ± 0</t>
+          <t xml:space="preserve">9.60901 ± 4.60567</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -8143,12 +8115,10 @@
       <c r="O113" t="n">
         <v>0.0</v>
       </c>
-      <c r="P113" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P113"/>
       <c r="Q113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R113" t="n">
@@ -9067,11 +9037,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R126" s="2" t="n">
@@ -9280,11 +9250,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P129" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R129" t="n">
@@ -9493,11 +9463,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -9705,12 +9675,10 @@
       <c r="O135" t="n">
         <v>0.0</v>
       </c>
-      <c r="P135" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P135"/>
       <c r="Q135" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -10629,11 +10597,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P148" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R148" s="2" t="n">
@@ -10842,11 +10810,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P151" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R151" t="n">
@@ -11055,11 +11023,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P154" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R154" s="2" t="n">
@@ -11267,12 +11235,10 @@
       <c r="O157" t="n">
         <v>0.0</v>
       </c>
-      <c r="P157" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P157"/>
       <c r="Q157" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R157" t="n">
@@ -12191,11 +12157,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P170" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R170" s="2" t="n">
@@ -12404,11 +12370,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P173" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R173" t="n">
@@ -12617,11 +12583,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P176" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R176" s="2" t="n">
@@ -12829,12 +12795,10 @@
       <c r="O179" t="n">
         <v>0.0</v>
       </c>
-      <c r="P179" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P179"/>
       <c r="Q179" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R179" t="n">
@@ -13753,11 +13717,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R192" s="2" t="n">
@@ -13966,11 +13930,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P195" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R195" t="n">
@@ -14179,11 +14143,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P198" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R198" s="2" t="n">
@@ -14391,12 +14355,10 @@
       <c r="O201" t="n">
         <v>0.0</v>
       </c>
-      <c r="P201" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P201"/>
       <c r="Q201" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R201" t="n">
@@ -15315,11 +15277,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P214" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R214" s="2" t="n">
@@ -15528,11 +15490,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P217" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R217" t="n">
@@ -15741,11 +15703,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P220" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R220" s="2" t="n">
@@ -15953,12 +15915,10 @@
       <c r="O223" t="n">
         <v>0.0</v>
       </c>
-      <c r="P223" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P223"/>
       <c r="Q223" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R223" t="n">
@@ -16877,11 +16837,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P236" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R236" s="2" t="n">
@@ -17090,11 +17050,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P239" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R239" t="n">
@@ -17303,11 +17263,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P242" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R242" s="2" t="n">
@@ -17515,12 +17475,10 @@
       <c r="O245" t="n">
         <v>0.0</v>
       </c>
-      <c r="P245" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P245"/>
       <c r="Q245" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R245" t="n">
@@ -18439,11 +18397,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P258" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R258" s="2" t="n">
@@ -18652,11 +18610,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P261" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R261" t="n">
@@ -18865,11 +18823,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P264" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R264" s="2" t="n">
@@ -19077,12 +19035,10 @@
       <c r="O267" t="n">
         <v>0.0</v>
       </c>
-      <c r="P267" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P267"/>
       <c r="Q267" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R267" t="n">
@@ -19290,12 +19246,10 @@
       <c r="O270" s="2" t="n">
         <v>0.770665587918015</v>
       </c>
-      <c r="P270" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P270" s="2"/>
       <c r="Q270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.770666 ± 0</t>
+          <t xml:space="preserve">0.770666</t>
         </is>
       </c>
       <c r="R270" s="2" t="n">
@@ -19361,12 +19315,10 @@
       <c r="O271" t="n">
         <v>0.029608017208390965</v>
       </c>
-      <c r="P271" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P271"/>
       <c r="Q271" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.029608 ± 0</t>
+          <t xml:space="preserve">0.029608</t>
         </is>
       </c>
       <c r="R271" t="n">
@@ -19432,12 +19384,10 @@
       <c r="O272" s="2" t="n">
         <v>0.8490976018837287</v>
       </c>
-      <c r="P272" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P272" s="2"/>
       <c r="Q272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.849098 ± 0</t>
+          <t xml:space="preserve">0.849098</t>
         </is>
       </c>
       <c r="R272" s="2" t="n">
@@ -19503,12 +19453,10 @@
       <c r="O273" t="n">
         <v>12.50151179072276</v>
       </c>
-      <c r="P273" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P273"/>
       <c r="Q273" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.5015 ± 0</t>
+          <t xml:space="preserve">12.5015</t>
         </is>
       </c>
       <c r="R273" t="n">
@@ -19574,12 +19522,10 @@
       <c r="O274" s="2" t="n">
         <v>0.7964197530864199</v>
       </c>
-      <c r="P274" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P274" s="2"/>
       <c r="Q274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.79642 ± 0</t>
+          <t xml:space="preserve">0.79642</t>
         </is>
       </c>
       <c r="R274" s="2" t="n">
@@ -19645,12 +19591,10 @@
       <c r="O275" t="n">
         <v>4.773443731055067</v>
       </c>
-      <c r="P275" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P275"/>
       <c r="Q275" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77344 ± 0</t>
+          <t xml:space="preserve">4.77344</t>
         </is>
       </c>
       <c r="R275" t="n">
@@ -19716,12 +19660,10 @@
       <c r="O276" s="2" t="n">
         <v>4.773443731055067</v>
       </c>
-      <c r="P276" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P276" s="2"/>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77344 ± 0</t>
+          <t xml:space="preserve">4.77344</t>
         </is>
       </c>
       <c r="R276" s="2" t="n">
@@ -19787,12 +19729,10 @@
       <c r="O277" t="n">
         <v>4.260656729701209</v>
       </c>
-      <c r="P277" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P277"/>
       <c r="Q277" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.26066 ± 0</t>
+          <t xml:space="preserve">4.26066</t>
         </is>
       </c>
       <c r="R277" t="n">
@@ -19858,12 +19798,10 @@
       <c r="O278" s="2" t="n">
         <v>0.9270333177979528</v>
       </c>
-      <c r="P278" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P278" s="2"/>
       <c r="Q278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927033 ± 0</t>
+          <t xml:space="preserve">0.927033</t>
         </is>
       </c>
       <c r="R278" s="2" t="n">
@@ -19930,11 +19868,11 @@
         <v>6.582174093992501</v>
       </c>
       <c r="P279" t="n">
-        <v>0.0</v>
+        <v>5.9850966597132444</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.58217 ± 0</t>
+          <t xml:space="preserve">6.58217 ± 5.9851</t>
         </is>
       </c>
       <c r="R279" t="n">
@@ -20001,11 +19939,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P280" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R280" s="2" t="n">
@@ -20072,11 +20010,11 @@
         <v>12.374335475594531</v>
       </c>
       <c r="P281" t="n">
-        <v>0.0</v>
+        <v>5.639433719545623</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.3743 ± 0</t>
+          <t xml:space="preserve">12.3743 ± 5.63943</t>
         </is>
       </c>
       <c r="R281" t="n">
@@ -20143,11 +20081,11 @@
         <v>0.9027790240778379</v>
       </c>
       <c r="P282" s="2" t="n">
-        <v>0.0</v>
+        <v>0.8715377486572258</v>
       </c>
       <c r="Q282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902779 ± 0</t>
+          <t xml:space="preserve">0.902779 ± 0.871538</t>
         </is>
       </c>
       <c r="R282" s="2" t="n">
@@ -20214,11 +20152,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P283" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R283" t="n">
@@ -20285,11 +20223,11 @@
         <v>-0.1496611213009582</v>
       </c>
       <c r="P284" s="2" t="n">
-        <v>0.0</v>
+        <v>0.8619610077873422</v>
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.149661 ± 0</t>
+          <t xml:space="preserve">-0.149661 ± 0.861961</t>
         </is>
       </c>
       <c r="R284" s="2" t="n">
@@ -20356,11 +20294,11 @@
         <v>8.093266346757641</v>
       </c>
       <c r="P285" t="n">
-        <v>0.0</v>
+        <v>7.358592654626764</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.09327 ± 0</t>
+          <t xml:space="preserve">8.09327 ± 7.35859</t>
         </is>
       </c>
       <c r="R285" t="n">
@@ -20427,11 +20365,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P286" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q286" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R286" s="2" t="n">
@@ -20498,11 +20436,11 @@
         <v>15.7868418118509</v>
       </c>
       <c r="P287" t="n">
-        <v>0.0</v>
+        <v>7.035005174473795</v>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.7868 ± 0</t>
+          <t xml:space="preserve">15.7868 ± 7.03501</t>
         </is>
       </c>
       <c r="R287" t="n">
@@ -20639,12 +20577,10 @@
       <c r="O289" t="n">
         <v>0.0</v>
       </c>
-      <c r="P289" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P289"/>
       <c r="Q289" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R289" t="n">
@@ -21563,11 +21499,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P302" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R302" s="2" t="n">
@@ -21776,11 +21712,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P305" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R305" t="n">
@@ -21989,11 +21925,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P308" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q308" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R308" s="2" t="n">
@@ -22201,12 +22137,10 @@
       <c r="O311" t="n">
         <v>0.0</v>
       </c>
-      <c r="P311" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P311"/>
       <c r="Q311" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R311" t="n">
@@ -23125,11 +23059,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P324" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R324" s="2" t="n">
@@ -23338,11 +23272,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P327" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R327" t="n">
@@ -23551,11 +23485,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P330" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q330" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R330" s="2" t="n">
@@ -23763,12 +23697,10 @@
       <c r="O333" t="n">
         <v>0.0</v>
       </c>
-      <c r="P333" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P333"/>
       <c r="Q333" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R333" t="n">
@@ -24687,11 +24619,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P346" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q346" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R346" s="2" t="n">
@@ -24900,11 +24832,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P349" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R349" t="n">
@@ -25113,11 +25045,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P352" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q352" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R352" s="2" t="n">
@@ -25325,12 +25257,10 @@
       <c r="O355" t="n">
         <v>0.0</v>
       </c>
-      <c r="P355" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P355"/>
       <c r="Q355" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R355" t="n">
@@ -26249,11 +26179,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P368" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q368" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R368" s="2" t="n">
@@ -26462,11 +26392,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P371" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R371" t="n">
@@ -26675,11 +26605,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P374" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q374" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R374" s="2" t="n">
@@ -26887,12 +26817,10 @@
       <c r="O377" t="n">
         <v>0.0</v>
       </c>
-      <c r="P377" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P377"/>
       <c r="Q377" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R377" t="n">
@@ -27811,11 +27739,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P390" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q390" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R390" s="2" t="n">
@@ -28024,11 +27952,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P393" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R393" t="n">
@@ -28237,11 +28165,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P396" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q396" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R396" s="2" t="n">
@@ -28449,12 +28377,10 @@
       <c r="O399" t="n">
         <v>0.0</v>
       </c>
-      <c r="P399" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P399"/>
       <c r="Q399" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R399" t="n">
@@ -29373,11 +29299,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P412" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q412" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R412" s="2" t="n">
@@ -29586,11 +29512,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P415" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R415" t="n">
@@ -29799,11 +29725,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P418" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q418" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R418" s="2" t="n">
@@ -30011,12 +29937,10 @@
       <c r="O421" t="n">
         <v>0.0</v>
       </c>
-      <c r="P421" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P421"/>
       <c r="Q421" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R421" t="n">
@@ -30935,11 +30859,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P434" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q434" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R434" s="2" t="n">
@@ -31148,11 +31072,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P437" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q437" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R437" t="n">
@@ -31361,11 +31285,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P440" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q440" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R440" s="2" t="n">
@@ -31573,12 +31497,10 @@
       <c r="O443" t="n">
         <v>0.0</v>
       </c>
-      <c r="P443" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P443"/>
       <c r="Q443" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R443" t="n">
@@ -31786,12 +31708,10 @@
       <c r="O446" s="2" t="n">
         <v>0.7611771986970685</v>
       </c>
-      <c r="P446" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P446" s="2"/>
       <c r="Q446" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.761177 ± 0</t>
+          <t xml:space="preserve">0.761177</t>
         </is>
       </c>
       <c r="R446" s="2" t="n">
@@ -31857,12 +31777,10 @@
       <c r="O447" t="n">
         <v>0.05848175743670013</v>
       </c>
-      <c r="P447" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P447"/>
       <c r="Q447" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0584818 ± 0</t>
+          <t xml:space="preserve">0.0584818</t>
         </is>
       </c>
       <c r="R447" t="n">
@@ -31928,12 +31846,10 @@
       <c r="O448" s="2" t="n">
         <v>0.8001880437833089</v>
       </c>
-      <c r="P448" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P448" s="2"/>
       <c r="Q448" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.800188 ± 0</t>
+          <t xml:space="preserve">0.800188</t>
         </is>
       </c>
       <c r="R448" s="2" t="n">
@@ -31999,12 +31915,10 @@
       <c r="O449" t="n">
         <v>6.538456381107492</v>
       </c>
-      <c r="P449" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P449"/>
       <c r="Q449" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.53846 ± 0</t>
+          <t xml:space="preserve">6.53846</t>
         </is>
       </c>
       <c r="R449" t="n">
@@ -32070,12 +31984,10 @@
       <c r="O450" s="2" t="n">
         <v>0.8809876543209876</v>
       </c>
-      <c r="P450" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P450" s="2"/>
       <c r="Q450" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.880988 ± 0</t>
+          <t xml:space="preserve">0.880988</t>
         </is>
       </c>
       <c r="R450" s="2" t="n">
@@ -32141,12 +32053,10 @@
       <c r="O451" t="n">
         <v>415.3891970836409</v>
       </c>
-      <c r="P451" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P451"/>
       <c r="Q451" t="inlineStr">
         <is>
-          <t xml:space="preserve">415.389 ± 0</t>
+          <t xml:space="preserve">415.389</t>
         </is>
       </c>
       <c r="R451" t="n">
@@ -32212,12 +32122,10 @@
       <c r="O452" s="2" t="n">
         <v>415.3891970836409</v>
       </c>
-      <c r="P452" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P452" s="2"/>
       <c r="Q452" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">415.389 ± 0</t>
+          <t xml:space="preserve">415.389</t>
         </is>
       </c>
       <c r="R452" s="2" t="n">
@@ -32283,12 +32191,10 @@
       <c r="O453" t="n">
         <v>339.0231341867594</v>
       </c>
-      <c r="P453" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P453"/>
       <c r="Q453" t="inlineStr">
         <is>
-          <t xml:space="preserve">339.023 ± 0</t>
+          <t xml:space="preserve">339.023</t>
         </is>
       </c>
       <c r="R453" t="n">
@@ -32354,12 +32260,10 @@
       <c r="O454" s="2" t="n">
         <v>0.939812263271673</v>
       </c>
-      <c r="P454" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P454" s="2"/>
       <c r="Q454" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.939812 ± 0</t>
+          <t xml:space="preserve">0.939812</t>
         </is>
       </c>
       <c r="R454" s="2" t="n">
@@ -32426,11 +32330,11 @@
         <v>2.01019545726001</v>
       </c>
       <c r="P455" t="n">
-        <v>0.0</v>
+        <v>0.4901707467643681</v>
       </c>
       <c r="Q455" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0102 ± 0</t>
+          <t xml:space="preserve">2.0102 ± 0.490171</t>
         </is>
       </c>
       <c r="R455" t="n">
@@ -32497,11 +32401,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P456" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q456" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R456" s="2" t="n">
@@ -32568,11 +32472,11 @@
         <v>2.913878983413816</v>
       </c>
       <c r="P457" t="n">
-        <v>0.0</v>
+        <v>0.04285118720798725</v>
       </c>
       <c r="Q457" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.91388 ± 0</t>
+          <t xml:space="preserve">2.91388 ± 0.0428512</t>
         </is>
       </c>
       <c r="R457" t="n">
@@ -32639,11 +32543,11 @@
         <v>0.08720070413467229</v>
       </c>
       <c r="P458" s="2" t="n">
-        <v>0.0</v>
+        <v>0.014971817370764312</v>
       </c>
       <c r="Q458" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0872007 ± 0</t>
+          <t xml:space="preserve">0.0872007 ± 0.0149718</t>
         </is>
       </c>
       <c r="R458" s="2" t="n">
@@ -32710,11 +32614,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P459" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q459" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R459" t="n">
@@ -32781,11 +32685,11 @@
         <v>0.8909013657394501</v>
       </c>
       <c r="P460" s="2" t="n">
-        <v>0.0</v>
+        <v>0.002501874074279764</v>
       </c>
       <c r="Q460" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.890901 ± 0</t>
+          <t xml:space="preserve">0.890901 ± 0.00250187</t>
         </is>
       </c>
       <c r="R460" s="2" t="n">
@@ -32852,11 +32756,11 @@
         <v>1.9572510092857862</v>
       </c>
       <c r="P461" t="n">
-        <v>0.0</v>
+        <v>0.5452965564360638</v>
       </c>
       <c r="Q461" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.95725 ± 0</t>
+          <t xml:space="preserve">1.95725 ± 0.545297</t>
         </is>
       </c>
       <c r="R461" t="n">
@@ -32923,11 +32827,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P462" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q462" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R462" s="2" t="n">
@@ -32994,11 +32898,11 @@
         <v>3.371957726067914</v>
       </c>
       <c r="P463" t="n">
-        <v>0.0</v>
+        <v>0.03867297152030222</v>
       </c>
       <c r="Q463" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.37196 ± 0</t>
+          <t xml:space="preserve">3.37196 ± 0.038673</t>
         </is>
       </c>
       <c r="R463" t="n">
@@ -33135,12 +33039,10 @@
       <c r="O465" t="n">
         <v>0.0</v>
       </c>
-      <c r="P465" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P465"/>
       <c r="Q465" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R465" t="n">
@@ -34059,11 +33961,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P478" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q478" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R478" s="2" t="n">
@@ -34272,11 +34174,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P481" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q481" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R481" t="n">
@@ -34485,11 +34387,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P484" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q484" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R484" s="2" t="n">
@@ -34697,12 +34599,10 @@
       <c r="O487" t="n">
         <v>0.0</v>
       </c>
-      <c r="P487" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P487"/>
       <c r="Q487" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R487" t="n">
@@ -35621,11 +35521,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P500" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q500" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R500" s="2" t="n">
@@ -35834,11 +35734,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P503" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q503" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R503" t="n">
@@ -36047,11 +35947,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P506" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q506" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R506" s="2" t="n">
@@ -36259,12 +36159,10 @@
       <c r="O509" t="n">
         <v>0.0</v>
       </c>
-      <c r="P509" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P509"/>
       <c r="Q509" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R509" t="n">
@@ -37183,11 +37081,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P522" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q522" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R522" s="2" t="n">
@@ -37396,11 +37294,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P525" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q525" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R525" t="n">
@@ -37609,11 +37507,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P528" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q528" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R528" s="2" t="n">
@@ -37821,12 +37719,10 @@
       <c r="O531" t="n">
         <v>0.0</v>
       </c>
-      <c r="P531" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P531"/>
       <c r="Q531" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R531" t="n">
@@ -38745,11 +38641,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P544" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q544" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R544" s="2" t="n">
@@ -38958,11 +38854,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P547" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q547" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R547" t="n">
@@ -39171,11 +39067,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P550" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q550" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R550" s="2" t="n">
@@ -39383,12 +39279,10 @@
       <c r="O553" t="n">
         <v>0.0</v>
       </c>
-      <c r="P553" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P553"/>
       <c r="Q553" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R553" t="n">
@@ -40307,11 +40201,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P566" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q566" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R566" s="2" t="n">
@@ -40520,11 +40414,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P569" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q569" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R569" t="n">
@@ -40733,11 +40627,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P572" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q572" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R572" s="2" t="n">
@@ -40945,12 +40839,10 @@
       <c r="O575" t="n">
         <v>0.0</v>
       </c>
-      <c r="P575" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P575"/>
       <c r="Q575" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R575" t="n">
@@ -41442,12 +41334,10 @@
       <c r="O582" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P582" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P582" s="2"/>
       <c r="Q582" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R582" s="2" t="n">
@@ -41869,11 +41759,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P588" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q588" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R588" s="2" t="n">
@@ -42082,11 +41972,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P591" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q591" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R591" t="n">
@@ -42295,11 +42185,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P594" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q594" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R594" s="2" t="n">
@@ -42507,12 +42397,10 @@
       <c r="O597" t="n">
         <v>0.0</v>
       </c>
-      <c r="P597" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P597"/>
       <c r="Q597" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R597" t="n">
@@ -43431,11 +43319,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P610" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q610" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R610" s="2" t="n">
@@ -43644,11 +43532,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P613" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q613" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R613" t="n">
@@ -43857,11 +43745,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P616" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q616" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R616" s="2" t="n">
@@ -44069,12 +43957,10 @@
       <c r="O619" t="n">
         <v>0.0</v>
       </c>
-      <c r="P619" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P619"/>
       <c r="Q619" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R619" t="n">
@@ -44282,12 +44168,10 @@
       <c r="O622" s="2" t="n">
         <v>0.52965</v>
       </c>
-      <c r="P622" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P622" s="2"/>
       <c r="Q622" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.52965 ± 0</t>
+          <t xml:space="preserve">0.52965</t>
         </is>
       </c>
       <c r="R622" s="2" t="n">
@@ -44353,12 +44237,10 @@
       <c r="O623" t="n">
         <v>0.42421363720633687</v>
       </c>
-      <c r="P623" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P623"/>
       <c r="Q623" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.424214 ± 0</t>
+          <t xml:space="preserve">0.424214</t>
         </is>
       </c>
       <c r="R623" t="n">
@@ -44424,12 +44306,10 @@
       <c r="O624" s="2" t="n">
         <v>0.5787031249999999</v>
       </c>
-      <c r="P624" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P624" s="2"/>
       <c r="Q624" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.578703 ± 0</t>
+          <t xml:space="preserve">0.578703</t>
         </is>
       </c>
       <c r="R624" s="2" t="n">
@@ -44495,12 +44375,10 @@
       <c r="O625" t="n">
         <v>61.45270668942703</v>
       </c>
-      <c r="P625" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P625"/>
       <c r="Q625" t="inlineStr">
         <is>
-          <t xml:space="preserve">61.4527 ± 0</t>
+          <t xml:space="preserve">61.4527</t>
         </is>
       </c>
       <c r="R625" t="n">
@@ -44566,12 +44444,10 @@
       <c r="O626" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P626" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P626" s="2"/>
       <c r="Q626" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R626" s="2" t="n">
@@ -44637,12 +44513,10 @@
       <c r="O627" t="n">
         <v>33.30069609009472</v>
       </c>
-      <c r="P627" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P627"/>
       <c r="Q627" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.3007 ± 0</t>
+          <t xml:space="preserve">33.3007</t>
         </is>
       </c>
       <c r="R627" t="n">
@@ -44708,12 +44582,10 @@
       <c r="O628" s="2" t="n">
         <v>33.30069609009472</v>
       </c>
-      <c r="P628" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P628" s="2"/>
       <c r="Q628" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.3007 ± 0</t>
+          <t xml:space="preserve">33.3007</t>
         </is>
       </c>
       <c r="R628" s="2" t="n">
@@ -44779,12 +44651,10 @@
       <c r="O629" t="n">
         <v>15.28110329348659</v>
       </c>
-      <c r="P629" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P629"/>
       <c r="Q629" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.2811 ± 0</t>
+          <t xml:space="preserve">15.2811</t>
         </is>
       </c>
       <c r="R629" t="n">
@@ -44850,12 +44720,10 @@
       <c r="O630" s="2" t="n">
         <v>0.8206064033763386</v>
       </c>
-      <c r="P630" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P630" s="2"/>
       <c r="Q630" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820606 ± 0</t>
+          <t xml:space="preserve">0.820606</t>
         </is>
       </c>
       <c r="R630" s="2" t="n">
@@ -44922,11 +44790,11 @@
         <v>15.363917670651059</v>
       </c>
       <c r="P631" t="n">
-        <v>0.0</v>
+        <v>29.22711247291791</v>
       </c>
       <c r="Q631" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.3639 ± 0</t>
+          <t xml:space="preserve">15.3639 ± 29.2271</t>
         </is>
       </c>
       <c r="R631" t="n">
@@ -44993,11 +44861,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P632" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q632" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R632" s="2" t="n">
@@ -45064,11 +44932,11 @@
         <v>1754.3857978552849</v>
       </c>
       <c r="P633" t="n">
-        <v>0.0</v>
+        <v>22.117752324650127</v>
       </c>
       <c r="Q633" t="inlineStr">
         <is>
-          <t xml:space="preserve">1754.39 ± 0</t>
+          <t xml:space="preserve">1754.39 ± 22.1178</t>
         </is>
       </c>
       <c r="R633" t="n">
@@ -45135,11 +45003,11 @@
         <v>0.01610295765320083</v>
       </c>
       <c r="P634" s="2" t="n">
-        <v>0.0</v>
+        <v>0.08981812831875627</v>
       </c>
       <c r="Q634" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.016103 ± 0</t>
+          <t xml:space="preserve">0.016103 ± 0.0898181</t>
         </is>
       </c>
       <c r="R634" s="2" t="n">
@@ -45206,11 +45074,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P635" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q635" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R635" t="n">
@@ -45277,11 +45145,11 @@
         <v>-0.08374332837863</v>
       </c>
       <c r="P636" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04030506250168554</v>
       </c>
       <c r="Q636" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0837433 ± 0</t>
+          <t xml:space="preserve">-0.0837433 ± 0.0403051</t>
         </is>
       </c>
       <c r="R636" s="2" t="n">
@@ -45348,11 +45216,11 @@
         <v>16.491714798673</v>
       </c>
       <c r="P637" t="n">
-        <v>0.0</v>
+        <v>86.36470582233898</v>
       </c>
       <c r="Q637" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.4917 ± 0</t>
+          <t xml:space="preserve">16.4917 ± 86.3647</t>
         </is>
       </c>
       <c r="R637" t="n">
@@ -45419,11 +45287,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P638" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q638" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R638" s="2" t="n">
@@ -45490,11 +45358,11 @@
         <v>2071.357530391925</v>
       </c>
       <c r="P639" t="n">
-        <v>0.0</v>
+        <v>38.454614264568704</v>
       </c>
       <c r="Q639" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071.36 ± 0</t>
+          <t xml:space="preserve">2071.36 ± 38.4546</t>
         </is>
       </c>
       <c r="R639" t="n">
@@ -45631,12 +45499,10 @@
       <c r="O641" t="n">
         <v>0.0</v>
       </c>
-      <c r="P641" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P641"/>
       <c r="Q641" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R641" t="n">
@@ -46555,11 +46421,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P654" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q654" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R654" s="2" t="n">
@@ -46768,11 +46634,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P657" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q657" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R657" t="n">
@@ -46981,11 +46847,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P660" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q660" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R660" s="2" t="n">
@@ -47193,12 +47059,10 @@
       <c r="O663" t="n">
         <v>0.0</v>
       </c>
-      <c r="P663" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P663"/>
       <c r="Q663" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R663" t="n">
@@ -48117,11 +47981,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P676" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q676" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R676" s="2" t="n">
@@ -48330,11 +48194,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P679" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q679" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R679" t="n">
@@ -48543,11 +48407,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P682" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q682" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R682" s="2" t="n">
@@ -48755,12 +48619,10 @@
       <c r="O685" t="n">
         <v>0.0</v>
       </c>
-      <c r="P685" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P685"/>
       <c r="Q685" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R685" t="n">
@@ -49679,11 +49541,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P698" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q698" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R698" s="2" t="n">
@@ -49892,11 +49754,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P701" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q701" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R701" t="n">
@@ -50105,11 +49967,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P704" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q704" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R704" s="2" t="n">
@@ -50317,12 +50179,10 @@
       <c r="O707" t="n">
         <v>0.0</v>
       </c>
-      <c r="P707" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P707"/>
       <c r="Q707" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R707" t="n">
@@ -50814,12 +50674,10 @@
       <c r="O714" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P714" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P714" s="2"/>
       <c r="Q714" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R714" s="2" t="n">
@@ -51241,11 +51099,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P720" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q720" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R720" s="2" t="n">
@@ -51454,11 +51312,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P723" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q723" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R723" t="n">
@@ -51667,11 +51525,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P726" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q726" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R726" s="2" t="n">
@@ -51879,12 +51737,10 @@
       <c r="O729" t="n">
         <v>0.0</v>
       </c>
-      <c r="P729" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P729"/>
       <c r="Q729" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R729" t="n">
@@ -52803,11 +52659,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P742" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q742" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R742" s="2" t="n">
@@ -53016,11 +52872,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P745" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q745" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R745" t="n">
@@ -53229,11 +53085,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P748" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q748" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R748" s="2" t="n">
@@ -53441,12 +53297,10 @@
       <c r="O751" t="n">
         <v>0.0</v>
       </c>
-      <c r="P751" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P751"/>
       <c r="Q751" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R751" t="n">
@@ -54365,11 +54219,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P764" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q764" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R764" s="2" t="n">
@@ -54578,11 +54432,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P767" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q767" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R767" t="n">
@@ -54791,11 +54645,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P770" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q770" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R770" s="2" t="n">
@@ -55003,12 +54857,10 @@
       <c r="O773" t="n">
         <v>0.0</v>
       </c>
-      <c r="P773" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P773"/>
       <c r="Q773" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R773" t="n">
@@ -55927,11 +55779,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P786" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q786" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R786" s="2" t="n">
@@ -56140,11 +55992,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P789" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q789" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R789" t="n">
@@ -56353,11 +56205,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P792" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q792" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R792" s="2" t="n">
@@ -56565,12 +56417,10 @@
       <c r="O795" t="n">
         <v>0.0</v>
       </c>
-      <c r="P795" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P795"/>
       <c r="Q795" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R795" t="n">
@@ -56778,12 +56628,10 @@
       <c r="O798" s="2" t="n">
         <v>0.9131975735479007</v>
       </c>
-      <c r="P798" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P798" s="2"/>
       <c r="Q798" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.913198 ± 0</t>
+          <t xml:space="preserve">0.913198</t>
         </is>
       </c>
       <c r="R798" s="2" t="n">
@@ -56849,12 +56697,10 @@
       <c r="O799" t="n">
         <v>0.015391049898669459</v>
       </c>
-      <c r="P799" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P799"/>
       <c r="Q799" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.015391 ± 0</t>
+          <t xml:space="preserve">0.015391</t>
         </is>
       </c>
       <c r="R799" t="n">
@@ -56920,12 +56766,10 @@
       <c r="O800" s="2" t="n">
         <v>0.6985660618611964</v>
       </c>
-      <c r="P800" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P800" s="2"/>
       <c r="Q800" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.698566 ± 0</t>
+          <t xml:space="preserve">0.698566</t>
         </is>
       </c>
       <c r="R800" s="2" t="n">
@@ -56991,12 +56835,10 @@
       <c r="O801" t="n">
         <v>1.1067540440868329</v>
       </c>
-      <c r="P801" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P801"/>
       <c r="Q801" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.10675 ± 0</t>
+          <t xml:space="preserve">1.10675</t>
         </is>
       </c>
       <c r="R801" t="n">
@@ -57062,12 +56904,10 @@
       <c r="O802" s="2" t="n">
         <v>0.5802469135802469</v>
       </c>
-      <c r="P802" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P802" s="2"/>
       <c r="Q802" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.580247 ± 0</t>
+          <t xml:space="preserve">0.580247</t>
         </is>
       </c>
       <c r="R802" s="2" t="n">
@@ -57133,12 +56973,10 @@
       <c r="O803" t="n">
         <v>6.261048531659883</v>
       </c>
-      <c r="P803" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P803"/>
       <c r="Q803" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.26105 ± 0</t>
+          <t xml:space="preserve">6.26105</t>
         </is>
       </c>
       <c r="R803" t="n">
@@ -57204,12 +57042,10 @@
       <c r="O804" s="2" t="n">
         <v>6.261048531659883</v>
       </c>
-      <c r="P804" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P804" s="2"/>
       <c r="Q804" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.26105 ± 0</t>
+          <t xml:space="preserve">6.26105</t>
         </is>
       </c>
       <c r="R804" s="2" t="n">
@@ -57275,12 +57111,10 @@
       <c r="O805" t="n">
         <v>5.766275112270799</v>
       </c>
-      <c r="P805" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P805"/>
       <c r="Q805" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.76628 ± 0</t>
+          <t xml:space="preserve">5.76628</t>
         </is>
       </c>
       <c r="R805" t="n">
@@ -57346,12 +57180,10 @@
       <c r="O806" s="2" t="n">
         <v>0.9203966264408556</v>
       </c>
-      <c r="P806" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P806" s="2"/>
       <c r="Q806" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.920397 ± 0</t>
+          <t xml:space="preserve">0.920397</t>
         </is>
       </c>
       <c r="R806" s="2" t="n">
@@ -57418,11 +57250,11 @@
         <v>4.04746190020483</v>
       </c>
       <c r="P807" t="n">
-        <v>0.0</v>
+        <v>1.2931948822784347</v>
       </c>
       <c r="Q807" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.04746 ± 0</t>
+          <t xml:space="preserve">4.04746 ± 1.29319</t>
         </is>
       </c>
       <c r="R807" t="n">
@@ -57489,11 +57321,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P808" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q808" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R808" s="2" t="n">
@@ -57560,11 +57392,11 @@
         <v>7.23017434437224</v>
       </c>
       <c r="P809" t="n">
-        <v>0.0</v>
+        <v>0.37613110913321485</v>
       </c>
       <c r="Q809" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.23017 ± 0</t>
+          <t xml:space="preserve">7.23017 ± 0.376131</t>
         </is>
       </c>
       <c r="R809" t="n">
@@ -57631,11 +57463,11 @@
         <v>0.3547480059005065</v>
       </c>
       <c r="P810" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05373184814046198</v>
       </c>
       <c r="Q810" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.354748 ± 0</t>
+          <t xml:space="preserve">0.354748 ± 0.0537318</t>
         </is>
       </c>
       <c r="R810" s="2" t="n">
@@ -57702,11 +57534,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P811" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q811" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R811" t="n">
@@ -57773,11 +57605,11 @@
         <v>0.4827027521449584</v>
       </c>
       <c r="P812" s="2" t="n">
-        <v>0.0</v>
+        <v>0.039289460494206535</v>
       </c>
       <c r="Q812" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.482703 ± 0</t>
+          <t xml:space="preserve">0.482703 ± 0.0392895</t>
         </is>
       </c>
       <c r="R812" s="2" t="n">
@@ -57844,11 +57676,11 @@
         <v>4.1752040520332</v>
       </c>
       <c r="P813" t="n">
-        <v>0.0</v>
+        <v>0.699174252212212</v>
       </c>
       <c r="Q813" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1752 ± 0</t>
+          <t xml:space="preserve">4.1752 ± 0.699174</t>
         </is>
       </c>
       <c r="R813" t="n">
@@ -57915,11 +57747,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P814" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q814" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R814" s="2" t="n">
@@ -57986,11 +57818,11 @@
         <v>9.435571216406363</v>
       </c>
       <c r="P815" t="n">
-        <v>0.0</v>
+        <v>0.35815272968587747</v>
       </c>
       <c r="Q815" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.43557 ± 0</t>
+          <t xml:space="preserve">9.43557 ± 0.358153</t>
         </is>
       </c>
       <c r="R815" t="n">
@@ -58127,12 +57959,10 @@
       <c r="O817" t="n">
         <v>0.0</v>
       </c>
-      <c r="P817" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P817"/>
       <c r="Q817" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R817" t="n">
@@ -59051,11 +58881,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P830" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q830" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R830" s="2" t="n">
@@ -59264,11 +59094,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P833" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q833" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R833" t="n">
@@ -59477,11 +59307,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P836" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q836" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R836" s="2" t="n">
@@ -59689,12 +59519,10 @@
       <c r="O839" t="n">
         <v>0.0</v>
       </c>
-      <c r="P839" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P839"/>
       <c r="Q839" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R839" t="n">
@@ -60613,11 +60441,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P852" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q852" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R852" s="2" t="n">
@@ -60826,11 +60654,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P855" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q855" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R855" t="n">
@@ -61039,11 +60867,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P858" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q858" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R858" s="2" t="n">
@@ -61251,12 +61079,10 @@
       <c r="O861" t="n">
         <v>0.0</v>
       </c>
-      <c r="P861" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P861"/>
       <c r="Q861" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R861" t="n">
@@ -62175,11 +62001,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P874" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q874" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R874" s="2" t="n">
@@ -62388,11 +62214,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P877" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q877" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R877" t="n">
@@ -62601,11 +62427,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P880" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q880" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R880" s="2" t="n">
@@ -62813,12 +62639,10 @@
       <c r="O883" t="n">
         <v>0.0</v>
       </c>
-      <c r="P883" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P883"/>
       <c r="Q883" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R883" t="n">
@@ -63737,11 +63561,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P896" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q896" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R896" s="2" t="n">
@@ -63950,11 +63774,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P899" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q899" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R899" t="n">
@@ -64163,11 +63987,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P902" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q902" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R902" s="2" t="n">
@@ -64375,12 +64199,10 @@
       <c r="O905" t="n">
         <v>0.0</v>
       </c>
-      <c r="P905" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P905"/>
       <c r="Q905" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R905" t="n">
@@ -64659,12 +64481,10 @@
       <c r="O909" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P909" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P909"/>
       <c r="Q909" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R909" t="n">
@@ -65299,11 +65119,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P918" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q918" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R918" s="2" t="n">
@@ -65512,11 +65332,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P921" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q921" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R921" t="n">
@@ -65725,11 +65545,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P924" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q924" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R924" s="2" t="n">
@@ -65937,12 +65757,10 @@
       <c r="O927" t="n">
         <v>0.0</v>
       </c>
-      <c r="P927" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P927"/>
       <c r="Q927" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R927" t="n">
@@ -66221,12 +66039,10 @@
       <c r="O931" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P931" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P931"/>
       <c r="Q931" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R931" t="n">
@@ -66861,11 +66677,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P940" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q940" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R940" s="2" t="n">
@@ -67074,11 +66890,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P943" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q943" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R943" t="n">
@@ -67287,11 +67103,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P946" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q946" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R946" s="2" t="n">
@@ -67499,12 +67315,10 @@
       <c r="O949" t="n">
         <v>0.0</v>
       </c>
-      <c r="P949" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P949"/>
       <c r="Q949" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R949" t="n">
@@ -68423,11 +68237,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P962" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q962" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R962" s="2" t="n">
@@ -68636,11 +68450,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P965" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q965" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R965" t="n">
@@ -68849,11 +68663,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P968" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q968" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R968" s="2" t="n">
@@ -69061,12 +68875,10 @@
       <c r="O971" t="n">
         <v>0.0</v>
       </c>
-      <c r="P971" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P971"/>
       <c r="Q971" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R971" t="n">
@@ -69274,12 +69086,10 @@
       <c r="O974" s="2" t="n">
         <v>0.619444612286002</v>
       </c>
-      <c r="P974" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P974" s="2"/>
       <c r="Q974" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.619445 ± 0</t>
+          <t xml:space="preserve">0.619445</t>
         </is>
       </c>
       <c r="R974" s="2" t="n">
@@ -69345,12 +69155,10 @@
       <c r="O975" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P975" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P975"/>
       <c r="Q975" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R975" t="n">
@@ -69416,12 +69224,10 @@
       <c r="O976" s="2" t="n">
         <v>0.8655543323682668</v>
       </c>
-      <c r="P976" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P976" s="2"/>
       <c r="Q976" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.865554 ± 0</t>
+          <t xml:space="preserve">0.865554</t>
         </is>
       </c>
       <c r="R976" s="2" t="n">
@@ -69487,12 +69293,10 @@
       <c r="O977" t="n">
         <v>64.00031021804406</v>
       </c>
-      <c r="P977" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P977"/>
       <c r="Q977" t="inlineStr">
         <is>
-          <t xml:space="preserve">64.0003 ± 0</t>
+          <t xml:space="preserve">64.0003</t>
         </is>
       </c>
       <c r="R977" t="n">
@@ -69558,12 +69362,10 @@
       <c r="O978" s="2" t="n">
         <v>0.9422222222222223</v>
       </c>
-      <c r="P978" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P978" s="2"/>
       <c r="Q978" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.942222 ± 0</t>
+          <t xml:space="preserve">0.942222</t>
         </is>
       </c>
       <c r="R978" s="2" t="n">
@@ -69771,12 +69573,10 @@
       <c r="O981" t="n">
         <v>15565.66017557031</v>
       </c>
-      <c r="P981" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P981"/>
       <c r="Q981" t="inlineStr">
         <is>
-          <t xml:space="preserve">15565.7 ± 0</t>
+          <t xml:space="preserve">15565.7</t>
         </is>
       </c>
       <c r="R981" t="n">
@@ -69842,12 +69642,10 @@
       <c r="O982" s="2" t="n">
         <v>0.9999401502175033</v>
       </c>
-      <c r="P982" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P982" s="2"/>
       <c r="Q982" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.99994 ± 0</t>
+          <t xml:space="preserve">0.99994</t>
         </is>
       </c>
       <c r="R982" s="2" t="n">
@@ -69914,11 +69712,11 @@
         <v>1.553241212660327</v>
       </c>
       <c r="P983" t="n">
-        <v>0.0</v>
+        <v>0.8049664160708678</v>
       </c>
       <c r="Q983" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.55324 ± 0</t>
+          <t xml:space="preserve">1.55324 ± 0.804966</t>
         </is>
       </c>
       <c r="R983" t="n">
@@ -69985,11 +69783,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P984" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q984" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R984" s="2" t="n">
@@ -70056,11 +69854,11 @@
         <v>6.32536924193509</v>
       </c>
       <c r="P985" t="n">
-        <v>0.0</v>
+        <v>0.5404484788989303</v>
       </c>
       <c r="Q985" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.32537 ± 0</t>
+          <t xml:space="preserve">6.32537 ± 0.540448</t>
         </is>
       </c>
       <c r="R985" t="n">
@@ -70127,11 +69925,11 @@
         <v>0.20431523386331302</v>
       </c>
       <c r="P986" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06230496116149596</v>
       </c>
       <c r="Q986" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.204315 ± 0</t>
+          <t xml:space="preserve">0.204315 ± 0.062305</t>
         </is>
       </c>
       <c r="R986" s="2" t="n">
@@ -70198,11 +69996,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P987" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q987" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R987" t="n">
@@ -70269,11 +70067,11 @@
         <v>0.5302727668614803</v>
       </c>
       <c r="P988" s="2" t="n">
-        <v>0.0</v>
+        <v>0.00862516832005052</v>
       </c>
       <c r="Q988" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.530273 ± 0</t>
+          <t xml:space="preserve">0.530273 ± 0.00862517</t>
         </is>
       </c>
       <c r="R988" s="2" t="n">
@@ -70340,11 +70138,11 @@
         <v>2.2475780087928205</v>
       </c>
       <c r="P989" t="n">
-        <v>0.0</v>
+        <v>0.7860253641842126</v>
       </c>
       <c r="Q989" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.24758 ± 0</t>
+          <t xml:space="preserve">2.24758 ± 0.786025</t>
         </is>
       </c>
       <c r="R989" t="n">
@@ -70411,11 +70209,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P990" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q990" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R990" s="2" t="n">
@@ -70482,11 +70280,11 @@
         <v>8.876660159144524</v>
       </c>
       <c r="P991" t="n">
-        <v>0.0</v>
+        <v>0.08094861643816746</v>
       </c>
       <c r="Q991" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.87666 ± 0</t>
+          <t xml:space="preserve">8.87666 ± 0.0809486</t>
         </is>
       </c>
       <c r="R991" t="n">
@@ -70623,12 +70421,10 @@
       <c r="O993" t="n">
         <v>0.0</v>
       </c>
-      <c r="P993" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P993"/>
       <c r="Q993" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R993" t="n">
@@ -70907,12 +70703,10 @@
       <c r="O997" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P997" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P997"/>
       <c r="Q997" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R997" t="n">
@@ -71547,11 +71341,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P1006" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q1006" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R1006" s="2" t="n">
@@ -71760,11 +71554,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P1009" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R1009" t="n">
@@ -71973,11 +71767,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P1012" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q1012" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R1012" s="2" t="n">
@@ -72185,12 +71979,10 @@
       <c r="O1015" t="n">
         <v>0.0</v>
       </c>
-      <c r="P1015" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P1015"/>
       <c r="Q1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R1015" t="n">
@@ -73109,11 +72901,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P1028" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q1028" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R1028" s="2" t="n">
@@ -73322,11 +73114,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P1031" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R1031" t="n">
@@ -73535,11 +73327,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P1034" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q1034" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R1034" s="2" t="n">
@@ -73747,12 +73539,10 @@
       <c r="O1037" t="n">
         <v>0.0</v>
       </c>
-      <c r="P1037" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P1037"/>
       <c r="Q1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R1037" t="n">
@@ -74671,11 +74461,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P1050" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q1050" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R1050" s="2" t="n">
@@ -74884,11 +74674,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P1053" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R1053" t="n">
@@ -75097,11 +74887,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P1056" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q1056" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R1056" s="2" t="n">
